--- a/erp-server/erp-server-oms/src/main/resources/excel/kolFeedbackTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolFeedbackTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -62,6 +76,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -77,6 +98,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1039,14 +1067,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="16.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="13.4545454545455" customWidth="1"/>
-    <col min="4" max="4" width="27.3636363636364" customWidth="1"/>
+    <col min="1" max="1" width="16.5416666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.725" customWidth="1"/>
+    <col min="3" max="3" width="13.4583333333333" customWidth="1"/>
+    <col min="4" max="4" width="27.3666666666667" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="7" width="17.4545454545455" customWidth="1"/>
+    <col min="7" max="7" width="17.4583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1073,9 +1101,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
-      <formula1>"抖音,微博,小红书,B站,Instagram,Youtube,TikTok,Facebook,X"</formula1>
+      <formula1>"长视频,图文,短视频,博客,杂志,动态"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1088,7 +1117,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1100,7 +1129,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
